--- a/Education/Secondary_School_Population_By_Age_Group.xlsx
+++ b/Education/Secondary_School_Population_By_Age_Group.xlsx
@@ -67,7 +67,7 @@
     <t>15 - 17 Years</t>
   </si>
   <si>
-    <t>11 Years &amp; Above</t>
+    <t>18 Years &amp; Above</t>
   </si>
   <si>
     <t>Male</t>
